--- a/Treinamento/Fiel (1).XLSX
+++ b/Treinamento/Fiel (1).XLSX
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$4233</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$238</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$Q$265</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
@@ -501,7 +501,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>130636399</v>
+        <v>130691413</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -516,10 +516,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="G2" s="1">
-        <v>45643</v>
+        <v>45647</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>130641195</v>
+        <v>130698913</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -569,10 +569,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="G3" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>130644493</v>
+        <v>130701542</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -622,10 +622,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="G4" s="1">
-        <v>45644</v>
+        <v>45647</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>130649220</v>
+        <v>129379286</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,10 +675,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45643</v>
+        <v>45553</v>
       </c>
       <c r="G5" s="1">
-        <v>45643</v>
+        <v>45554</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -687,7 +687,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>130651339</v>
+        <v>130492413</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -728,10 +728,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45644</v>
+        <v>45632</v>
       </c>
       <c r="G6" s="1">
-        <v>45644</v>
+        <v>45633</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -740,7 +740,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>130653303</v>
+        <v>130492730</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -781,10 +781,10 @@
         <v>1211</v>
       </c>
       <c r="F7" s="1">
-        <v>45644</v>
+        <v>45632</v>
       </c>
       <c r="G7" s="1">
-        <v>45645</v>
+        <v>45633</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>130659030</v>
+        <v>130521238</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -834,10 +834,10 @@
         <v>1211</v>
       </c>
       <c r="F8" s="1">
-        <v>45644</v>
+        <v>45635</v>
       </c>
       <c r="G8" s="1">
-        <v>45644</v>
+        <v>45636</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -846,7 +846,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>130665661</v>
+        <v>130554065</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -884,13 +884,13 @@
         <v>17</v>
       </c>
       <c r="E9">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45644</v>
+        <v>45637</v>
       </c>
       <c r="G9" s="1">
-        <v>45645</v>
+        <v>45638</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -899,7 +899,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>130665670</v>
+        <v>126525165</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -940,10 +940,10 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45644</v>
+        <v>45647</v>
       </c>
       <c r="G10" s="1">
-        <v>45644</v>
+        <v>45649</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>130672884</v>
+        <v>126533954</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -990,13 +990,13 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F11" s="1">
         <v>45645</v>
       </c>
       <c r="G11" s="1">
-        <v>45645</v>
+        <v>45649</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1005,7 +1005,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>130678604</v>
+        <v>126611411</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1046,10 +1046,10 @@
         <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45645</v>
+        <v>45649</v>
       </c>
       <c r="G12" s="1">
-        <v>45645</v>
+        <v>45649</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1058,7 +1058,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>130681889</v>
+        <v>126629775</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1096,13 +1096,13 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45645</v>
+        <v>45649</v>
       </c>
       <c r="G13" s="1">
-        <v>45645</v>
+        <v>45649</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1111,7 +1111,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K13" t="s">
         <v>17</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>130688161</v>
+        <v>126632188</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,7 +1152,7 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="G14" s="1">
         <v>45646</v>
@@ -1164,7 +1164,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>129379286</v>
+        <v>126641761</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1205,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45553</v>
+        <v>45649</v>
       </c>
       <c r="G15" s="1">
-        <v>45554</v>
+        <v>45649</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1217,7 +1217,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>130492413</v>
+        <v>126676192</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1258,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45632</v>
+        <v>45649</v>
       </c>
       <c r="G16" s="1">
-        <v>45633</v>
+        <v>45649</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1270,7 +1270,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K16" t="s">
         <v>17</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>130492730</v>
+        <v>126685658</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1311,10 +1311,10 @@
         <v>1211</v>
       </c>
       <c r="F17" s="1">
-        <v>45632</v>
+        <v>45650</v>
       </c>
       <c r="G17" s="1">
-        <v>45633</v>
+        <v>45650</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1323,7 +1323,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K17" t="s">
         <v>17</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>130521238</v>
+        <v>126685907</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1364,10 +1364,10 @@
         <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45635</v>
+        <v>45647</v>
       </c>
       <c r="G18" s="1">
-        <v>45636</v>
+        <v>45647</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1376,7 +1376,7 @@
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K18" t="s">
         <v>17</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>130553435</v>
+        <v>126704281</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1417,10 +1417,10 @@
         <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45637</v>
+        <v>45650</v>
       </c>
       <c r="G19" s="1">
-        <v>45638</v>
+        <v>45650</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1429,7 +1429,7 @@
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K19" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>130554065</v>
+        <v>126742171</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1470,10 +1470,10 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45637</v>
+        <v>45649</v>
       </c>
       <c r="G20" s="1">
-        <v>45638</v>
+        <v>45649</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1482,7 +1482,7 @@
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K20" t="s">
         <v>17</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>126348533</v>
+        <v>126772945</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1520,13 +1520,13 @@
         <v>17</v>
       </c>
       <c r="E21">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F21" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G21" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>126632188</v>
+        <v>126798944</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1576,10 +1576,10 @@
         <v>1211</v>
       </c>
       <c r="F22" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G22" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>126666778</v>
+        <v>126832622</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1629,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G23" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>126685907</v>
+        <v>126862552</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1682,10 +1682,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="G24" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>126799081</v>
+        <v>126875217</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,10 +1735,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G25" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>126862552</v>
+        <v>126947977</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1788,10 +1788,10 @@
         <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="G26" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>126987607</v>
+        <v>126974438</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1947,10 +1947,10 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="G29" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>127019281</v>
+        <v>126987607</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127268682</v>
+        <v>127221334</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2156,13 +2156,13 @@
         <v>17</v>
       </c>
       <c r="E33">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G33" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127274032</v>
+        <v>127223445</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2212,10 +2212,10 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="G34" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127275980</v>
+        <v>127224681</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2265,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G35" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127323110</v>
+        <v>127268682</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2315,7 +2315,7 @@
         <v>17</v>
       </c>
       <c r="E36">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F36" s="1">
         <v>45646</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127328503</v>
+        <v>127274032</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127329438</v>
+        <v>127275980</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,10 +2424,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="G38" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127408289</v>
+        <v>127323110</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2477,10 +2477,10 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="G39" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>127428124</v>
+        <v>127328503</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2530,10 +2530,10 @@
         <v>1211</v>
       </c>
       <c r="F40" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="G40" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>127429804</v>
+        <v>127329438</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2580,7 +2580,7 @@
         <v>17</v>
       </c>
       <c r="E41">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="1">
         <v>45647</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>127497766</v>
+        <v>127374101</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2636,10 +2636,10 @@
         <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G42" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>127591543</v>
+        <v>127377244</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,10 +2689,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45643</v>
+        <v>45651</v>
       </c>
       <c r="G43" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>127654384</v>
+        <v>127408289</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2742,7 +2742,7 @@
         <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45645</v>
+        <v>45647</v>
       </c>
       <c r="G44" s="1">
         <v>45647</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>127810990</v>
+        <v>127428124</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,10 +2795,10 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="G45" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>127832401</v>
+        <v>127429804</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2845,13 +2845,13 @@
         <v>17</v>
       </c>
       <c r="E46">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F46" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="G46" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>127847032</v>
+        <v>127497766</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>127922146</v>
+        <v>127517402</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2951,13 +2951,13 @@
         <v>17</v>
       </c>
       <c r="E48">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G48" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>128077584</v>
+        <v>127522608</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3007,10 +3007,10 @@
         <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="G49" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>128226781</v>
+        <v>127525116</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3060,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G50" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>128230583</v>
+        <v>127544426</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3113,10 +3113,10 @@
         <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G51" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>128318246</v>
+        <v>127547674</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3166,10 +3166,10 @@
         <v>1211</v>
       </c>
       <c r="F52" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="G52" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>128437383</v>
+        <v>127589719</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3219,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G53" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>128460441</v>
+        <v>127592960</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3272,10 +3272,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="G54" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>128465549</v>
+        <v>127676121</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3325,10 +3325,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45645</v>
+        <v>45650</v>
       </c>
       <c r="G55" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>128468953</v>
+        <v>127725714</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3378,10 +3378,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="G56" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>128600368</v>
+        <v>127799646</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3431,10 +3431,10 @@
         <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G57" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>128643435</v>
+        <v>127810990</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>128651443</v>
+        <v>127832401</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>128702299</v>
+        <v>127843753</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3587,13 +3587,13 @@
         <v>17</v>
       </c>
       <c r="E60">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>45643</v>
+        <v>45649</v>
       </c>
       <c r="G60" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>128882723</v>
+        <v>127847032</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3643,10 +3643,10 @@
         <v>1211</v>
       </c>
       <c r="F61" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="G61" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>128894566</v>
+        <v>127849636</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3693,13 +3693,13 @@
         <v>17</v>
       </c>
       <c r="E62">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G62" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129157974</v>
+        <v>127868963</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3749,10 +3749,10 @@
         <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45647</v>
+        <v>45650</v>
       </c>
       <c r="G63" s="1">
-        <v>45647</v>
+        <v>45650</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129173085</v>
+        <v>127877304</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3802,10 +3802,10 @@
         <v>1211</v>
       </c>
       <c r="F64" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="G64" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129180089</v>
+        <v>127922146</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3852,13 +3852,13 @@
         <v>17</v>
       </c>
       <c r="E65">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F65" s="1">
         <v>45646</v>
       </c>
       <c r="G65" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129181179</v>
+        <v>127980137</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3908,10 +3908,10 @@
         <v>1211</v>
       </c>
       <c r="F66" s="1">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="G66" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129237891</v>
+        <v>127991088</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3958,13 +3958,13 @@
         <v>17</v>
       </c>
       <c r="E67">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F67" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="G67" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129258168</v>
+        <v>127991901</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4014,10 +4014,10 @@
         <v>1211</v>
       </c>
       <c r="F68" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G68" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129271984</v>
+        <v>127991990</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4067,10 +4067,10 @@
         <v>1211</v>
       </c>
       <c r="F69" s="1">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="G69" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129293215</v>
+        <v>128043604</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4120,10 +4120,10 @@
         <v>1211</v>
       </c>
       <c r="F70" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G70" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129353355</v>
+        <v>128077584</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4173,7 +4173,7 @@
         <v>1211</v>
       </c>
       <c r="F71" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="G71" s="1">
         <v>45646</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129434315</v>
+        <v>128137310</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4226,10 +4226,10 @@
         <v>1211</v>
       </c>
       <c r="F72" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G72" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129536353</v>
+        <v>128196088</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4279,10 +4279,10 @@
         <v>1211</v>
       </c>
       <c r="F73" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="G73" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129556234</v>
+        <v>128206608</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4332,10 +4332,10 @@
         <v>1211</v>
       </c>
       <c r="F74" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G74" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129668042</v>
+        <v>128226781</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4385,7 +4385,7 @@
         <v>1211</v>
       </c>
       <c r="F75" s="1">
-        <v>45642</v>
+        <v>45646</v>
       </c>
       <c r="G75" s="1">
         <v>45646</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129697421</v>
+        <v>128230583</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129700113</v>
+        <v>128282346</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4491,10 +4491,10 @@
         <v>1211</v>
       </c>
       <c r="F77" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G77" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129802033</v>
+        <v>128287670</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4544,10 +4544,10 @@
         <v>1211</v>
       </c>
       <c r="F78" s="1">
-        <v>45643</v>
+        <v>45650</v>
       </c>
       <c r="G78" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129883098</v>
+        <v>128316601</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4597,10 +4597,10 @@
         <v>1211</v>
       </c>
       <c r="F79" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G79" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129930241</v>
+        <v>128329361</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4650,10 +4650,10 @@
         <v>1211</v>
       </c>
       <c r="F80" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G80" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129936500</v>
+        <v>128335369</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4703,10 +4703,10 @@
         <v>1211</v>
       </c>
       <c r="F81" s="1">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="G81" s="1">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129949333</v>
+        <v>128388977</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4756,10 +4756,10 @@
         <v>1211</v>
       </c>
       <c r="F82" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G82" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>130049796</v>
+        <v>128437383</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4809,7 +4809,7 @@
         <v>1211</v>
       </c>
       <c r="F83" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="G83" s="1">
         <v>45646</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>130056115</v>
+        <v>128442814</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4862,10 +4862,10 @@
         <v>1211</v>
       </c>
       <c r="F84" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="G84" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>130081754</v>
+        <v>128460441</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>130144432</v>
+        <v>128468953</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4968,7 +4968,7 @@
         <v>1211</v>
       </c>
       <c r="F86" s="1">
-        <v>45644</v>
+        <v>45646</v>
       </c>
       <c r="G86" s="1">
         <v>45646</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>130147497</v>
+        <v>128474183</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5021,10 +5021,10 @@
         <v>1211</v>
       </c>
       <c r="F87" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G87" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -5059,7 +5059,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>130156222</v>
+        <v>128485687</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5074,10 +5074,10 @@
         <v>1211</v>
       </c>
       <c r="F88" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="G88" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>130198878</v>
+        <v>128600368</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5130,7 +5130,7 @@
         <v>45646</v>
       </c>
       <c r="G89" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>130248036</v>
+        <v>128643435</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5180,10 +5180,10 @@
         <v>1211</v>
       </c>
       <c r="F90" s="1">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="G90" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>130304367</v>
+        <v>128651443</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>130314326</v>
+        <v>128708182</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5286,10 +5286,10 @@
         <v>1211</v>
       </c>
       <c r="F92" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G92" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>130320664</v>
+        <v>128803681</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5339,10 +5339,10 @@
         <v>1211</v>
       </c>
       <c r="F93" s="1">
-        <v>45647</v>
+        <v>45650</v>
       </c>
       <c r="G93" s="1">
-        <v>45647</v>
+        <v>45650</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>130339209</v>
+        <v>128824257</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5389,13 +5389,13 @@
         <v>17</v>
       </c>
       <c r="E94">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F94" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G94" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>130375125</v>
+        <v>128882723</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5445,10 +5445,10 @@
         <v>1211</v>
       </c>
       <c r="F95" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="G95" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>130381655</v>
+        <v>128894566</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -5495,13 +5495,13 @@
         <v>17</v>
       </c>
       <c r="E96">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F96" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="G96" s="1">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -5536,7 +5536,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>130396121</v>
+        <v>128948113</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -5551,10 +5551,10 @@
         <v>1211</v>
       </c>
       <c r="F97" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G97" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>130397032</v>
+        <v>128962763</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -5604,10 +5604,10 @@
         <v>1211</v>
       </c>
       <c r="F98" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G98" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>130459349</v>
+        <v>128993358</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -5657,10 +5657,10 @@
         <v>1211</v>
       </c>
       <c r="F99" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G99" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>130472008</v>
+        <v>129008824</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -5710,10 +5710,10 @@
         <v>1211</v>
       </c>
       <c r="F100" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="G100" s="1">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>130475458</v>
+        <v>129157974</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>130505975</v>
+        <v>129173085</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -5813,7 +5813,7 @@
         <v>17</v>
       </c>
       <c r="E102">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F102" s="1">
         <v>45646</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>130508613</v>
+        <v>129180089</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>130542733</v>
+        <v>129181179</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>130549014</v>
+        <v>129201021</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -5975,10 +5975,10 @@
         <v>1211</v>
       </c>
       <c r="F105" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G105" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -6013,7 +6013,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>130561445</v>
+        <v>129234108</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -6028,10 +6028,10 @@
         <v>1211</v>
       </c>
       <c r="F106" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G106" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>130591898</v>
+        <v>129237891</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -6081,10 +6081,10 @@
         <v>1211</v>
       </c>
       <c r="F107" s="1">
-        <v>45639</v>
+        <v>45646</v>
       </c>
       <c r="G107" s="1">
-        <v>45639</v>
+        <v>45646</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -6119,7 +6119,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>130613319</v>
+        <v>129258168</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -6137,7 +6137,7 @@
         <v>45646</v>
       </c>
       <c r="G108" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>130630714</v>
+        <v>129271984</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>130645437</v>
+        <v>129293215</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>130646275</v>
+        <v>129366291</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
@@ -6293,10 +6293,10 @@
         <v>1211</v>
       </c>
       <c r="F111" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G111" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>130657577</v>
+        <v>129381650</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -6346,10 +6346,10 @@
         <v>1211</v>
       </c>
       <c r="F112" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G112" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>130659064</v>
+        <v>129396624</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -6399,10 +6399,10 @@
         <v>1211</v>
       </c>
       <c r="F113" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G113" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>130663424</v>
+        <v>129434315</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -6449,7 +6449,7 @@
         <v>17</v>
       </c>
       <c r="E114">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F114" s="1">
         <v>45646</v>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>130684207</v>
+        <v>129482111</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
@@ -6505,10 +6505,10 @@
         <v>1211</v>
       </c>
       <c r="F115" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G115" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>130686450</v>
+        <v>129512416</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
@@ -6558,10 +6558,10 @@
         <v>1211</v>
       </c>
       <c r="F116" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G116" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>130689234</v>
+        <v>129536353</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
@@ -6611,10 +6611,10 @@
         <v>1211</v>
       </c>
       <c r="F117" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="G117" s="1">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>130699258</v>
+        <v>129556234</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>130699996</v>
+        <v>129616973</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
@@ -6714,13 +6714,13 @@
         <v>17</v>
       </c>
       <c r="E119">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F119" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G119" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>130709211</v>
+        <v>129627939</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
@@ -6767,13 +6767,13 @@
         <v>17</v>
       </c>
       <c r="E120">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F120" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="G120" s="1">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -6808,7 +6808,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>130715666</v>
+        <v>129697421</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
@@ -6820,13 +6820,13 @@
         <v>17</v>
       </c>
       <c r="E121">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F121" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G121" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -6861,7 +6861,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>130715668</v>
+        <v>129700113</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
@@ -6876,10 +6876,10 @@
         <v>1211</v>
       </c>
       <c r="F122" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G122" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>130715676</v>
+        <v>129747171</v>
       </c>
       <c r="B123" t="s">
         <v>17</v>
@@ -6926,13 +6926,13 @@
         <v>17</v>
       </c>
       <c r="E123">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="F123" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G123" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>130715680</v>
+        <v>129800249</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -6979,13 +6979,13 @@
         <v>17</v>
       </c>
       <c r="E124">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F124" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G124" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -7020,7 +7020,7 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>130715691</v>
+        <v>129841314</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -7035,10 +7035,10 @@
         <v>1211</v>
       </c>
       <c r="F125" s="1">
-        <v>45648</v>
+        <v>45644</v>
       </c>
       <c r="G125" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>130715699</v>
+        <v>129883098</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
@@ -7085,13 +7085,13 @@
         <v>17</v>
       </c>
       <c r="E126">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F126" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G126" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -7126,7 +7126,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>130715709</v>
+        <v>129930241</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
@@ -7141,10 +7141,10 @@
         <v>1211</v>
       </c>
       <c r="F127" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G127" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -7179,7 +7179,7 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>130715710</v>
+        <v>129936500</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
@@ -7194,10 +7194,10 @@
         <v>1211</v>
       </c>
       <c r="F128" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G128" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>130715715</v>
+        <v>129949333</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
@@ -7247,10 +7247,10 @@
         <v>1211</v>
       </c>
       <c r="F129" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G129" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -7285,7 +7285,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>130715721</v>
+        <v>130056115</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
@@ -7300,10 +7300,10 @@
         <v>1211</v>
       </c>
       <c r="F130" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="G130" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>130715723</v>
+        <v>130081754</v>
       </c>
       <c r="B131" t="s">
         <v>17</v>
@@ -7353,10 +7353,10 @@
         <v>1211</v>
       </c>
       <c r="F131" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G131" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -7391,7 +7391,7 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>130715729</v>
+        <v>130122948</v>
       </c>
       <c r="B132" t="s">
         <v>17</v>
@@ -7406,10 +7406,10 @@
         <v>1211</v>
       </c>
       <c r="F132" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G132" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>130715733</v>
+        <v>130130360</v>
       </c>
       <c r="B133" t="s">
         <v>17</v>
@@ -7459,10 +7459,10 @@
         <v>1211</v>
       </c>
       <c r="F133" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G133" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>130715736</v>
+        <v>130130539</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
@@ -7512,10 +7512,10 @@
         <v>1211</v>
       </c>
       <c r="F134" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G134" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -7550,7 +7550,7 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>130715741</v>
+        <v>130147497</v>
       </c>
       <c r="B135" t="s">
         <v>17</v>
@@ -7565,10 +7565,10 @@
         <v>1211</v>
       </c>
       <c r="F135" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G135" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>130715742</v>
+        <v>130161717</v>
       </c>
       <c r="B136" t="s">
         <v>17</v>
@@ -7618,10 +7618,10 @@
         <v>1211</v>
       </c>
       <c r="F136" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G136" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -7656,7 +7656,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>130715749</v>
+        <v>130183951</v>
       </c>
       <c r="B137" t="s">
         <v>17</v>
@@ -7671,10 +7671,10 @@
         <v>1211</v>
       </c>
       <c r="F137" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G137" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>130715752</v>
+        <v>130198878</v>
       </c>
       <c r="B138" t="s">
         <v>17</v>
@@ -7724,10 +7724,10 @@
         <v>1211</v>
       </c>
       <c r="F138" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G138" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>130715753</v>
+        <v>130283293</v>
       </c>
       <c r="B139" t="s">
         <v>17</v>
@@ -7774,13 +7774,13 @@
         <v>17</v>
       </c>
       <c r="E139">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F139" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G139" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -7815,7 +7815,7 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>130715755</v>
+        <v>130304367</v>
       </c>
       <c r="B140" t="s">
         <v>17</v>
@@ -7827,13 +7827,13 @@
         <v>17</v>
       </c>
       <c r="E140">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F140" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G140" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>130715757</v>
+        <v>130314326</v>
       </c>
       <c r="B141" t="s">
         <v>17</v>
@@ -7883,10 +7883,10 @@
         <v>1211</v>
       </c>
       <c r="F141" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G141" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>130715760</v>
+        <v>130320664</v>
       </c>
       <c r="B142" t="s">
         <v>17</v>
@@ -7936,10 +7936,10 @@
         <v>1211</v>
       </c>
       <c r="F142" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="G142" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -7974,7 +7974,7 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>130715781</v>
+        <v>130338803</v>
       </c>
       <c r="B143" t="s">
         <v>17</v>
@@ -7989,10 +7989,10 @@
         <v>1211</v>
       </c>
       <c r="F143" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G143" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -8027,7 +8027,7 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>130715785</v>
+        <v>130339209</v>
       </c>
       <c r="B144" t="s">
         <v>17</v>
@@ -8042,10 +8042,10 @@
         <v>1211</v>
       </c>
       <c r="F144" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G144" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -8080,7 +8080,7 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>130715812</v>
+        <v>130375125</v>
       </c>
       <c r="B145" t="s">
         <v>17</v>
@@ -8095,10 +8095,10 @@
         <v>1211</v>
       </c>
       <c r="F145" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G145" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -8133,7 +8133,7 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>130715834</v>
+        <v>130380421</v>
       </c>
       <c r="B146" t="s">
         <v>17</v>
@@ -8148,10 +8148,10 @@
         <v>1211</v>
       </c>
       <c r="F146" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G146" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>130715837</v>
+        <v>130381655</v>
       </c>
       <c r="B147" t="s">
         <v>17</v>
@@ -8201,10 +8201,10 @@
         <v>1211</v>
       </c>
       <c r="F147" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="G147" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -8239,7 +8239,7 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>130715844</v>
+        <v>130396121</v>
       </c>
       <c r="B148" t="s">
         <v>17</v>
@@ -8254,10 +8254,10 @@
         <v>1211</v>
       </c>
       <c r="F148" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G148" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -8292,7 +8292,7 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>130715877</v>
+        <v>130397032</v>
       </c>
       <c r="B149" t="s">
         <v>17</v>
@@ -8307,10 +8307,10 @@
         <v>1211</v>
       </c>
       <c r="F149" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G149" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -8345,7 +8345,7 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>130715881</v>
+        <v>130410787</v>
       </c>
       <c r="B150" t="s">
         <v>17</v>
@@ -8357,13 +8357,13 @@
         <v>17</v>
       </c>
       <c r="E150">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F150" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G150" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -8398,7 +8398,7 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>130715882</v>
+        <v>130454527</v>
       </c>
       <c r="B151" t="s">
         <v>17</v>
@@ -8413,10 +8413,10 @@
         <v>1211</v>
       </c>
       <c r="F151" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="G151" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -8451,7 +8451,7 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>130715885</v>
+        <v>130457920</v>
       </c>
       <c r="B152" t="s">
         <v>17</v>
@@ -8466,10 +8466,10 @@
         <v>1211</v>
       </c>
       <c r="F152" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G152" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -8504,7 +8504,7 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>130715887</v>
+        <v>130459065</v>
       </c>
       <c r="B153" t="s">
         <v>17</v>
@@ -8516,13 +8516,13 @@
         <v>17</v>
       </c>
       <c r="E153">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F153" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="G153" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="H153" t="s">
         <v>17</v>
@@ -8557,7 +8557,7 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>130715891</v>
+        <v>130459349</v>
       </c>
       <c r="B154" t="s">
         <v>17</v>
@@ -8572,10 +8572,10 @@
         <v>1211</v>
       </c>
       <c r="F154" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G154" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -8610,7 +8610,7 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>130715898</v>
+        <v>130472008</v>
       </c>
       <c r="B155" t="s">
         <v>17</v>
@@ -8625,10 +8625,10 @@
         <v>1211</v>
       </c>
       <c r="F155" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="G155" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="H155" t="s">
         <v>17</v>
@@ -8663,7 +8663,7 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>130715900</v>
+        <v>130475458</v>
       </c>
       <c r="B156" t="s">
         <v>17</v>
@@ -8678,10 +8678,10 @@
         <v>1211</v>
       </c>
       <c r="F156" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="G156" s="1">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="H156" t="s">
         <v>17</v>
@@ -8716,7 +8716,7 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>130715910</v>
+        <v>130480861</v>
       </c>
       <c r="B157" t="s">
         <v>17</v>
@@ -8728,13 +8728,13 @@
         <v>17</v>
       </c>
       <c r="E157">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F157" s="1">
-        <v>45648</v>
+        <v>45645</v>
       </c>
       <c r="G157" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>130715923</v>
+        <v>130503079</v>
       </c>
       <c r="B158" t="s">
         <v>17</v>
@@ -8784,10 +8784,10 @@
         <v>1211</v>
       </c>
       <c r="F158" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G158" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -8822,7 +8822,7 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>130715929</v>
+        <v>130505975</v>
       </c>
       <c r="B159" t="s">
         <v>17</v>
@@ -8834,13 +8834,13 @@
         <v>17</v>
       </c>
       <c r="E159">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F159" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G159" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -8875,7 +8875,7 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>130715942</v>
+        <v>130508613</v>
       </c>
       <c r="B160" t="s">
         <v>17</v>
@@ -8890,10 +8890,10 @@
         <v>1211</v>
       </c>
       <c r="F160" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G160" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>130715953</v>
+        <v>130510737</v>
       </c>
       <c r="B161" t="s">
         <v>17</v>
@@ -8940,13 +8940,13 @@
         <v>17</v>
       </c>
       <c r="E161">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F161" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G161" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -8981,7 +8981,7 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>130715988</v>
+        <v>130541383</v>
       </c>
       <c r="B162" t="s">
         <v>17</v>
@@ -8996,10 +8996,10 @@
         <v>1211</v>
       </c>
       <c r="F162" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G162" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -9034,7 +9034,7 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>130716024</v>
+        <v>130542733</v>
       </c>
       <c r="B163" t="s">
         <v>17</v>
@@ -9049,10 +9049,10 @@
         <v>1211</v>
       </c>
       <c r="F163" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G163" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -9087,7 +9087,7 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>130716047</v>
+        <v>130549014</v>
       </c>
       <c r="B164" t="s">
         <v>17</v>
@@ -9102,10 +9102,10 @@
         <v>1211</v>
       </c>
       <c r="F164" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G164" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>130716056</v>
+        <v>130561193</v>
       </c>
       <c r="B165" t="s">
         <v>17</v>
@@ -9152,13 +9152,13 @@
         <v>17</v>
       </c>
       <c r="E165">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F165" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G165" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -9193,7 +9193,7 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>130716062</v>
+        <v>130561445</v>
       </c>
       <c r="B166" t="s">
         <v>17</v>
@@ -9208,10 +9208,10 @@
         <v>1211</v>
       </c>
       <c r="F166" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G166" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -9246,7 +9246,7 @@
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>130716094</v>
+        <v>130562570</v>
       </c>
       <c r="B167" t="s">
         <v>17</v>
@@ -9261,10 +9261,10 @@
         <v>1211</v>
       </c>
       <c r="F167" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G167" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -9299,7 +9299,7 @@
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>130716101</v>
+        <v>130591898</v>
       </c>
       <c r="B168" t="s">
         <v>17</v>
@@ -9314,10 +9314,10 @@
         <v>1211</v>
       </c>
       <c r="F168" s="1">
-        <v>45648</v>
+        <v>45639</v>
       </c>
       <c r="G168" s="1">
-        <v>45648</v>
+        <v>45639</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>130716111</v>
+        <v>130605444</v>
       </c>
       <c r="B169" t="s">
         <v>17</v>
@@ -9367,10 +9367,10 @@
         <v>1211</v>
       </c>
       <c r="F169" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G169" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>130716138</v>
+        <v>130613319</v>
       </c>
       <c r="B170" t="s">
         <v>17</v>
@@ -9420,10 +9420,10 @@
         <v>1211</v>
       </c>
       <c r="F170" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G170" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>130716139</v>
+        <v>130630714</v>
       </c>
       <c r="B171" t="s">
         <v>17</v>
@@ -9473,10 +9473,10 @@
         <v>1211</v>
       </c>
       <c r="F171" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G171" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -9511,7 +9511,7 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>130716142</v>
+        <v>130639657</v>
       </c>
       <c r="B172" t="s">
         <v>17</v>
@@ -9526,10 +9526,10 @@
         <v>1211</v>
       </c>
       <c r="F172" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G172" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -9564,7 +9564,7 @@
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>130716149</v>
+        <v>130641901</v>
       </c>
       <c r="B173" t="s">
         <v>17</v>
@@ -9576,13 +9576,13 @@
         <v>17</v>
       </c>
       <c r="E173">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F173" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G173" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -9617,7 +9617,7 @@
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>130716154</v>
+        <v>130645437</v>
       </c>
       <c r="B174" t="s">
         <v>17</v>
@@ -9632,10 +9632,10 @@
         <v>1211</v>
       </c>
       <c r="F174" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G174" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>130716164</v>
+        <v>130646275</v>
       </c>
       <c r="B175" t="s">
         <v>17</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>130716215</v>
+        <v>130654219</v>
       </c>
       <c r="B176" t="s">
         <v>17</v>
@@ -9738,10 +9738,10 @@
         <v>1211</v>
       </c>
       <c r="F176" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="G176" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -9776,7 +9776,7 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>130716221</v>
+        <v>130657577</v>
       </c>
       <c r="B177" t="s">
         <v>17</v>
@@ -9788,13 +9788,13 @@
         <v>17</v>
       </c>
       <c r="E177">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F177" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G177" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -9829,7 +9829,7 @@
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>130716234</v>
+        <v>130659064</v>
       </c>
       <c r="B178" t="s">
         <v>17</v>
@@ -9841,13 +9841,13 @@
         <v>17</v>
       </c>
       <c r="E178">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F178" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G178" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -9882,7 +9882,7 @@
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>130716258</v>
+        <v>130663424</v>
       </c>
       <c r="B179" t="s">
         <v>17</v>
@@ -9894,13 +9894,13 @@
         <v>17</v>
       </c>
       <c r="E179">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F179" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G179" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -9935,7 +9935,7 @@
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>130716307</v>
+        <v>130663938</v>
       </c>
       <c r="B180" t="s">
         <v>17</v>
@@ -9950,10 +9950,10 @@
         <v>1211</v>
       </c>
       <c r="F180" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G180" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -9988,7 +9988,7 @@
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>130716321</v>
+        <v>130668625</v>
       </c>
       <c r="B181" t="s">
         <v>17</v>
@@ -10000,13 +10000,13 @@
         <v>17</v>
       </c>
       <c r="E181">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F181" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G181" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -10041,7 +10041,7 @@
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>130716323</v>
+        <v>130684207</v>
       </c>
       <c r="B182" t="s">
         <v>17</v>
@@ -10056,10 +10056,10 @@
         <v>1211</v>
       </c>
       <c r="F182" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G182" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H182" t="s">
         <v>17</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>130716326</v>
+        <v>130685676</v>
       </c>
       <c r="B183" t="s">
         <v>17</v>
@@ -10109,10 +10109,10 @@
         <v>1211</v>
       </c>
       <c r="F183" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G183" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -10147,7 +10147,7 @@
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>130716351</v>
+        <v>130686185</v>
       </c>
       <c r="B184" t="s">
         <v>17</v>
@@ -10159,13 +10159,13 @@
         <v>17</v>
       </c>
       <c r="E184">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F184" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G184" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H184" t="s">
         <v>17</v>
@@ -10200,7 +10200,7 @@
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>130716399</v>
+        <v>130686450</v>
       </c>
       <c r="B185" t="s">
         <v>17</v>
@@ -10215,10 +10215,10 @@
         <v>1211</v>
       </c>
       <c r="F185" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G185" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H185" t="s">
         <v>17</v>
@@ -10253,7 +10253,7 @@
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>130716402</v>
+        <v>130689234</v>
       </c>
       <c r="B186" t="s">
         <v>17</v>
@@ -10268,10 +10268,10 @@
         <v>1211</v>
       </c>
       <c r="F186" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G186" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H186" t="s">
         <v>17</v>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>130716430</v>
+        <v>130699258</v>
       </c>
       <c r="B187" t="s">
         <v>17</v>
@@ -10318,13 +10318,13 @@
         <v>17</v>
       </c>
       <c r="E187">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F187" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G187" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H187" t="s">
         <v>17</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>130716445</v>
+        <v>130699996</v>
       </c>
       <c r="B188" t="s">
         <v>17</v>
@@ -10371,13 +10371,13 @@
         <v>17</v>
       </c>
       <c r="E188">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F188" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G188" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H188" t="s">
         <v>17</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>130716446</v>
+        <v>130702209</v>
       </c>
       <c r="B189" t="s">
         <v>17</v>
@@ -10424,13 +10424,13 @@
         <v>17</v>
       </c>
       <c r="E189">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F189" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G189" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H189" t="s">
         <v>17</v>
@@ -10465,7 +10465,7 @@
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>130716474</v>
+        <v>130703244</v>
       </c>
       <c r="B190" t="s">
         <v>17</v>
@@ -10480,10 +10480,10 @@
         <v>1212</v>
       </c>
       <c r="F190" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G190" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H190" t="s">
         <v>17</v>
@@ -10518,7 +10518,7 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>130716479</v>
+        <v>130704903</v>
       </c>
       <c r="B191" t="s">
         <v>17</v>
@@ -10533,10 +10533,10 @@
         <v>1211</v>
       </c>
       <c r="F191" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G191" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H191" t="s">
         <v>17</v>
@@ -10571,7 +10571,7 @@
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>130716480</v>
+        <v>130705265</v>
       </c>
       <c r="B192" t="s">
         <v>17</v>
@@ -10586,10 +10586,10 @@
         <v>1211</v>
       </c>
       <c r="F192" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G192" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H192" t="s">
         <v>17</v>
@@ -10624,7 +10624,7 @@
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>130716500</v>
+        <v>130706487</v>
       </c>
       <c r="B193" t="s">
         <v>17</v>
@@ -10636,13 +10636,13 @@
         <v>17</v>
       </c>
       <c r="E193">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F193" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G193" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H193" t="s">
         <v>17</v>
@@ -10677,7 +10677,7 @@
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>130716513</v>
+        <v>130709211</v>
       </c>
       <c r="B194" t="s">
         <v>17</v>
@@ -10689,13 +10689,13 @@
         <v>17</v>
       </c>
       <c r="E194">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F194" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="G194" s="1">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="H194" t="s">
         <v>17</v>
@@ -10730,7 +10730,7 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>130716516</v>
+        <v>130710482</v>
       </c>
       <c r="B195" t="s">
         <v>17</v>
@@ -10745,10 +10745,10 @@
         <v>1211</v>
       </c>
       <c r="F195" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="G195" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="H195" t="s">
         <v>17</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>130716531</v>
+        <v>130718286</v>
       </c>
       <c r="B196" t="s">
         <v>17</v>
@@ -10798,10 +10798,10 @@
         <v>1211</v>
       </c>
       <c r="F196" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="G196" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="H196" t="s">
         <v>17</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>130716533</v>
+        <v>130721692</v>
       </c>
       <c r="B197" t="s">
         <v>17</v>
@@ -10848,13 +10848,13 @@
         <v>17</v>
       </c>
       <c r="E197">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F197" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G197" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H197" t="s">
         <v>17</v>
@@ -10889,7 +10889,7 @@
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>130716556</v>
+        <v>130726766</v>
       </c>
       <c r="B198" t="s">
         <v>17</v>
@@ -10901,13 +10901,13 @@
         <v>17</v>
       </c>
       <c r="E198">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F198" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="G198" s="1">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="H198" t="s">
         <v>17</v>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>130716558</v>
+        <v>130728321</v>
       </c>
       <c r="B199" t="s">
         <v>17</v>
@@ -10957,10 +10957,10 @@
         <v>1211</v>
       </c>
       <c r="F199" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="G199" s="1">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="H199" t="s">
         <v>17</v>
@@ -10995,7 +10995,7 @@
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>130716575</v>
+        <v>130739594</v>
       </c>
       <c r="B200" t="s">
         <v>17</v>
@@ -11007,13 +11007,13 @@
         <v>17</v>
       </c>
       <c r="E200">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F200" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G200" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H200" t="s">
         <v>17</v>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>130716583</v>
+        <v>130739595</v>
       </c>
       <c r="B201" t="s">
         <v>17</v>
@@ -11060,13 +11060,13 @@
         <v>17</v>
       </c>
       <c r="E201">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F201" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G201" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H201" t="s">
         <v>17</v>
@@ -11101,7 +11101,7 @@
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>130716603</v>
+        <v>130739608</v>
       </c>
       <c r="B202" t="s">
         <v>17</v>
@@ -11113,13 +11113,13 @@
         <v>17</v>
       </c>
       <c r="E202">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F202" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G202" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H202" t="s">
         <v>17</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>130716642</v>
+        <v>130739621</v>
       </c>
       <c r="B203" t="s">
         <v>17</v>
@@ -11169,10 +11169,10 @@
         <v>1211</v>
       </c>
       <c r="F203" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G203" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H203" t="s">
         <v>17</v>
@@ -11207,7 +11207,7 @@
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>130716657</v>
+        <v>130739625</v>
       </c>
       <c r="B204" t="s">
         <v>17</v>
@@ -11222,10 +11222,10 @@
         <v>1211</v>
       </c>
       <c r="F204" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G204" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H204" t="s">
         <v>17</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>130716662</v>
+        <v>130739628</v>
       </c>
       <c r="B205" t="s">
         <v>17</v>
@@ -11272,13 +11272,13 @@
         <v>17</v>
       </c>
       <c r="E205">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F205" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G205" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H205" t="s">
         <v>17</v>
@@ -11313,7 +11313,7 @@
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>130716701</v>
+        <v>130739641</v>
       </c>
       <c r="B206" t="s">
         <v>17</v>
@@ -11328,10 +11328,10 @@
         <v>1211</v>
       </c>
       <c r="F206" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G206" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H206" t="s">
         <v>17</v>
@@ -11366,7 +11366,7 @@
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>130716707</v>
+        <v>130739660</v>
       </c>
       <c r="B207" t="s">
         <v>17</v>
@@ -11381,10 +11381,10 @@
         <v>1211</v>
       </c>
       <c r="F207" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G207" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H207" t="s">
         <v>17</v>
@@ -11419,7 +11419,7 @@
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>130716712</v>
+        <v>130739662</v>
       </c>
       <c r="B208" t="s">
         <v>17</v>
@@ -11434,10 +11434,10 @@
         <v>1211</v>
       </c>
       <c r="F208" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G208" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H208" t="s">
         <v>17</v>
@@ -11472,7 +11472,7 @@
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>130716740</v>
+        <v>130739663</v>
       </c>
       <c r="B209" t="s">
         <v>17</v>
@@ -11487,10 +11487,10 @@
         <v>2013</v>
       </c>
       <c r="F209" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G209" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H209" t="s">
         <v>17</v>
@@ -11525,7 +11525,7 @@
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>130716764</v>
+        <v>130739678</v>
       </c>
       <c r="B210" t="s">
         <v>17</v>
@@ -11540,10 +11540,10 @@
         <v>1211</v>
       </c>
       <c r="F210" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G210" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H210" t="s">
         <v>17</v>
@@ -11578,7 +11578,7 @@
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>130716774</v>
+        <v>130739682</v>
       </c>
       <c r="B211" t="s">
         <v>17</v>
@@ -11593,10 +11593,10 @@
         <v>1211</v>
       </c>
       <c r="F211" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="G211" s="1">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="H211" t="s">
         <v>17</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>130716778</v>
+        <v>130739688</v>
       </c>
       <c r="B212" t="s">
         <v>17</v>
@@ -11643,13 +11643,13 @@
         <v>17</v>
       </c>
       <c r="E212">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F212" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="G212" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="H212" t="s">
         <v>17</v>
@@ -11684,7 +11684,7 @@
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>130716783</v>
+        <v>130739723</v>
       </c>
       <c r="B213" t="s">
         <v>17</v>
@@ -11699,10 +11699,10 @@
         <v>1211</v>
       </c>
       <c r="F213" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="G213" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="H213" t="s">
         <v>17</v>
@@ -11737,7 +11737,7 @@
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>130716786</v>
+        <v>130739755</v>
       </c>
       <c r="B214" t="s">
         <v>17</v>
@@ -11752,10 +11752,10 @@
         <v>1211</v>
       </c>
       <c r="F214" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="G214" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="H214" t="s">
         <v>17</v>
@@ -11790,7 +11790,7 @@
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>130716812</v>
+        <v>130739757</v>
       </c>
       <c r="B215" t="s">
         <v>17</v>
@@ -11802,13 +11802,13 @@
         <v>17</v>
       </c>
       <c r="E215">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F215" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="G215" s="1">
-        <v>45649</v>
+        <v>45651</v>
       </c>
       <c r="H215" t="s">
         <v>17</v>
@@ -11843,7 +11843,7 @@
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>129379286</v>
+        <v>130739784</v>
       </c>
       <c r="B216" t="s">
         <v>17</v>
@@ -11858,10 +11858,10 @@
         <v>1211</v>
       </c>
       <c r="F216" s="1">
-        <v>45553</v>
+        <v>45651</v>
       </c>
       <c r="G216" s="1">
-        <v>45554</v>
+        <v>45651</v>
       </c>
       <c r="H216" t="s">
         <v>17</v>
@@ -11870,7 +11870,7 @@
         <v>42</v>
       </c>
       <c r="J216">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K216" t="s">
         <v>17</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>130492413</v>
+        <v>130739799</v>
       </c>
       <c r="B217" t="s">
         <v>17</v>
@@ -11911,10 +11911,10 @@
         <v>1211</v>
       </c>
       <c r="F217" s="1">
-        <v>45632</v>
+        <v>45651</v>
       </c>
       <c r="G217" s="1">
-        <v>45633</v>
+        <v>45651</v>
       </c>
       <c r="H217" t="s">
         <v>17</v>
@@ -11923,7 +11923,7 @@
         <v>42</v>
       </c>
       <c r="J217">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K217" t="s">
         <v>17</v>
@@ -11949,7 +11949,7 @@
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>130492730</v>
+        <v>130739808</v>
       </c>
       <c r="B218" t="s">
         <v>17</v>
@@ -11961,13 +11961,13 @@
         <v>17</v>
       </c>
       <c r="E218">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F218" s="1">
-        <v>45632</v>
+        <v>45651</v>
       </c>
       <c r="G218" s="1">
-        <v>45633</v>
+        <v>45651</v>
       </c>
       <c r="H218" t="s">
         <v>17</v>
@@ -11976,7 +11976,7 @@
         <v>42</v>
       </c>
       <c r="J218">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K218" t="s">
         <v>17</v>
@@ -12002,7 +12002,7 @@
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>130521238</v>
+        <v>130739810</v>
       </c>
       <c r="B219" t="s">
         <v>17</v>
@@ -12017,10 +12017,10 @@
         <v>1211</v>
       </c>
       <c r="F219" s="1">
-        <v>45635</v>
+        <v>45651</v>
       </c>
       <c r="G219" s="1">
-        <v>45636</v>
+        <v>45651</v>
       </c>
       <c r="H219" t="s">
         <v>17</v>
@@ -12029,7 +12029,7 @@
         <v>42</v>
       </c>
       <c r="J219">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K219" t="s">
         <v>17</v>
@@ -12055,7 +12055,7 @@
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>130553435</v>
+        <v>130739829</v>
       </c>
       <c r="B220" t="s">
         <v>17</v>
@@ -12070,10 +12070,10 @@
         <v>1211</v>
       </c>
       <c r="F220" s="1">
-        <v>45637</v>
+        <v>45651</v>
       </c>
       <c r="G220" s="1">
-        <v>45638</v>
+        <v>45651</v>
       </c>
       <c r="H220" t="s">
         <v>17</v>
@@ -12082,7 +12082,7 @@
         <v>42</v>
       </c>
       <c r="J220">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K220" t="s">
         <v>17</v>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>130554065</v>
+        <v>130739865</v>
       </c>
       <c r="B221" t="s">
         <v>17</v>
@@ -12123,10 +12123,10 @@
         <v>1211</v>
       </c>
       <c r="F221" s="1">
-        <v>45637</v>
+        <v>45651</v>
       </c>
       <c r="G221" s="1">
-        <v>45638</v>
+        <v>45651</v>
       </c>
       <c r="H221" t="s">
         <v>17</v>
@@ -12135,7 +12135,7 @@
         <v>42</v>
       </c>
       <c r="J221">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K221" t="s">
         <v>17</v>
@@ -12161,7 +12161,7 @@
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>130665982</v>
+        <v>130739867</v>
       </c>
       <c r="B222" t="s">
         <v>17</v>
@@ -12176,10 +12176,10 @@
         <v>2013</v>
       </c>
       <c r="F222" s="1">
-        <v>45644</v>
+        <v>45651</v>
       </c>
       <c r="G222" s="1">
-        <v>45645</v>
+        <v>45651</v>
       </c>
       <c r="H222" t="s">
         <v>17</v>
@@ -12188,7 +12188,7 @@
         <v>42</v>
       </c>
       <c r="J222">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K222" t="s">
         <v>17</v>
@@ -12214,7 +12214,7 @@
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>130708995</v>
+        <v>130739915</v>
       </c>
       <c r="B223" t="s">
         <v>17</v>
@@ -12226,13 +12226,13 @@
         <v>17</v>
       </c>
       <c r="E223">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F223" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G223" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H223" t="s">
         <v>17</v>
@@ -12241,7 +12241,7 @@
         <v>42</v>
       </c>
       <c r="J223">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K223" t="s">
         <v>17</v>
@@ -12267,7 +12267,7 @@
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>130691564</v>
+        <v>130739916</v>
       </c>
       <c r="B224" t="s">
         <v>17</v>
@@ -12279,13 +12279,13 @@
         <v>17</v>
       </c>
       <c r="E224">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F224" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G224" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H224" t="s">
         <v>17</v>
@@ -12294,7 +12294,7 @@
         <v>42</v>
       </c>
       <c r="J224">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K224" t="s">
         <v>17</v>
@@ -12320,7 +12320,7 @@
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>130691585</v>
+        <v>130739919</v>
       </c>
       <c r="B225" t="s">
         <v>17</v>
@@ -12332,13 +12332,13 @@
         <v>17</v>
       </c>
       <c r="E225">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F225" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G225" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H225" t="s">
         <v>17</v>
@@ -12347,7 +12347,7 @@
         <v>42</v>
       </c>
       <c r="J225">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K225" t="s">
         <v>17</v>
@@ -12373,7 +12373,7 @@
     </row>
     <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>130691596</v>
+        <v>130739928</v>
       </c>
       <c r="B226" t="s">
         <v>17</v>
@@ -12385,13 +12385,13 @@
         <v>17</v>
       </c>
       <c r="E226">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F226" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G226" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H226" t="s">
         <v>17</v>
@@ -12400,7 +12400,7 @@
         <v>42</v>
       </c>
       <c r="J226">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K226" t="s">
         <v>17</v>
@@ -12426,7 +12426,7 @@
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>130691601</v>
+        <v>130739975</v>
       </c>
       <c r="B227" t="s">
         <v>17</v>
@@ -12438,13 +12438,13 @@
         <v>17</v>
       </c>
       <c r="E227">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F227" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G227" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H227" t="s">
         <v>17</v>
@@ -12453,7 +12453,7 @@
         <v>42</v>
       </c>
       <c r="J227">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K227" t="s">
         <v>17</v>
@@ -12479,7 +12479,7 @@
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>130691608</v>
+        <v>130739978</v>
       </c>
       <c r="B228" t="s">
         <v>17</v>
@@ -12494,10 +12494,10 @@
         <v>2013</v>
       </c>
       <c r="F228" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G228" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H228" t="s">
         <v>17</v>
@@ -12506,7 +12506,7 @@
         <v>42</v>
       </c>
       <c r="J228">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K228" t="s">
         <v>17</v>
@@ -12532,7 +12532,7 @@
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>130692257</v>
+        <v>130739991</v>
       </c>
       <c r="B229" t="s">
         <v>17</v>
@@ -12547,10 +12547,10 @@
         <v>2013</v>
       </c>
       <c r="F229" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G229" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H229" t="s">
         <v>17</v>
@@ -12559,7 +12559,7 @@
         <v>42</v>
       </c>
       <c r="J229">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K229" t="s">
         <v>17</v>
@@ -12585,7 +12585,7 @@
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>130692460</v>
+        <v>130739996</v>
       </c>
       <c r="B230" t="s">
         <v>17</v>
@@ -12600,10 +12600,10 @@
         <v>2013</v>
       </c>
       <c r="F230" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G230" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H230" t="s">
         <v>17</v>
@@ -12612,7 +12612,7 @@
         <v>42</v>
       </c>
       <c r="J230">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K230" t="s">
         <v>17</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>130697160</v>
+        <v>130740000</v>
       </c>
       <c r="B231" t="s">
         <v>17</v>
@@ -12650,13 +12650,13 @@
         <v>17</v>
       </c>
       <c r="E231">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F231" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G231" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H231" t="s">
         <v>17</v>
@@ -12665,7 +12665,7 @@
         <v>42</v>
       </c>
       <c r="J231">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K231" t="s">
         <v>17</v>
@@ -12691,7 +12691,7 @@
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>130697551</v>
+        <v>130740005</v>
       </c>
       <c r="B232" t="s">
         <v>17</v>
@@ -12706,10 +12706,10 @@
         <v>2013</v>
       </c>
       <c r="F232" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G232" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="H232" t="s">
         <v>17</v>
@@ -12718,7 +12718,7 @@
         <v>42</v>
       </c>
       <c r="J232">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K232" t="s">
         <v>17</v>
@@ -12744,7 +12744,7 @@
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>130702244</v>
+        <v>130740047</v>
       </c>
       <c r="B233" t="s">
         <v>17</v>
@@ -12756,13 +12756,13 @@
         <v>17</v>
       </c>
       <c r="E233">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F233" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G233" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H233" t="s">
         <v>17</v>
@@ -12771,7 +12771,7 @@
         <v>42</v>
       </c>
       <c r="J233">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K233" t="s">
         <v>17</v>
@@ -12797,7 +12797,7 @@
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>130703610</v>
+        <v>130740051</v>
       </c>
       <c r="B234" t="s">
         <v>17</v>
@@ -12809,13 +12809,13 @@
         <v>17</v>
       </c>
       <c r="E234">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F234" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G234" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H234" t="s">
         <v>17</v>
@@ -12824,7 +12824,7 @@
         <v>42</v>
       </c>
       <c r="J234">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K234" t="s">
         <v>17</v>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>130704784</v>
+        <v>130740057</v>
       </c>
       <c r="B235" t="s">
         <v>17</v>
@@ -12862,13 +12862,13 @@
         <v>17</v>
       </c>
       <c r="E235">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F235" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G235" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H235" t="s">
         <v>17</v>
@@ -12877,7 +12877,7 @@
         <v>42</v>
       </c>
       <c r="J235">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K235" t="s">
         <v>17</v>
@@ -12903,7 +12903,7 @@
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>130705222</v>
+        <v>130740058</v>
       </c>
       <c r="B236" t="s">
         <v>17</v>
@@ -12918,10 +12918,10 @@
         <v>2013</v>
       </c>
       <c r="F236" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G236" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H236" t="s">
         <v>17</v>
@@ -12930,7 +12930,7 @@
         <v>42</v>
       </c>
       <c r="J236">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K236" t="s">
         <v>17</v>
@@ -12956,7 +12956,7 @@
     </row>
     <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>130705907</v>
+        <v>130740093</v>
       </c>
       <c r="B237" t="s">
         <v>17</v>
@@ -12968,13 +12968,13 @@
         <v>17</v>
       </c>
       <c r="E237">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F237" s="1">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="G237" s="1">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="H237" t="s">
         <v>17</v>
@@ -12983,7 +12983,7 @@
         <v>42</v>
       </c>
       <c r="J237">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K237" t="s">
         <v>17</v>
@@ -13009,7 +13009,7 @@
     </row>
     <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>130707051</v>
+        <v>130740120</v>
       </c>
       <c r="B238" t="s">
         <v>17</v>
@@ -13024,39 +13024,1470 @@
         <v>2013</v>
       </c>
       <c r="F238" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G238" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H238" t="s">
+        <v>17</v>
+      </c>
+      <c r="I238">
+        <v>42</v>
+      </c>
+      <c r="J238">
+        <v>8001</v>
+      </c>
+      <c r="K238" t="s">
+        <v>17</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <v>0</v>
+      </c>
+      <c r="P238">
+        <v>0</v>
+      </c>
+      <c r="Q238">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>130740155</v>
+      </c>
+      <c r="B239" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239" t="s">
+        <v>17</v>
+      </c>
+      <c r="D239" t="s">
+        <v>17</v>
+      </c>
+      <c r="E239">
+        <v>1211</v>
+      </c>
+      <c r="F239" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G239" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H239" t="s">
+        <v>17</v>
+      </c>
+      <c r="I239">
+        <v>42</v>
+      </c>
+      <c r="J239">
+        <v>8001</v>
+      </c>
+      <c r="K239" t="s">
+        <v>17</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>0</v>
+      </c>
+      <c r="P239">
+        <v>0</v>
+      </c>
+      <c r="Q239">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>130740181</v>
+      </c>
+      <c r="B240" t="s">
+        <v>17</v>
+      </c>
+      <c r="C240" t="s">
+        <v>17</v>
+      </c>
+      <c r="D240" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240">
+        <v>2013</v>
+      </c>
+      <c r="F240" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G240" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H240" t="s">
+        <v>17</v>
+      </c>
+      <c r="I240">
+        <v>42</v>
+      </c>
+      <c r="J240">
+        <v>8001</v>
+      </c>
+      <c r="K240" t="s">
+        <v>17</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>0</v>
+      </c>
+      <c r="O240">
+        <v>0</v>
+      </c>
+      <c r="P240">
+        <v>0</v>
+      </c>
+      <c r="Q240">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>130740186</v>
+      </c>
+      <c r="B241" t="s">
+        <v>17</v>
+      </c>
+      <c r="C241" t="s">
+        <v>17</v>
+      </c>
+      <c r="D241" t="s">
+        <v>17</v>
+      </c>
+      <c r="E241">
+        <v>1211</v>
+      </c>
+      <c r="F241" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G241" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H241" t="s">
+        <v>17</v>
+      </c>
+      <c r="I241">
+        <v>42</v>
+      </c>
+      <c r="J241">
+        <v>8001</v>
+      </c>
+      <c r="K241" t="s">
+        <v>17</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>0</v>
+      </c>
+      <c r="O241">
+        <v>0</v>
+      </c>
+      <c r="P241">
+        <v>0</v>
+      </c>
+      <c r="Q241">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>130740204</v>
+      </c>
+      <c r="B242" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242" t="s">
+        <v>17</v>
+      </c>
+      <c r="D242" t="s">
+        <v>17</v>
+      </c>
+      <c r="E242">
+        <v>1211</v>
+      </c>
+      <c r="F242" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G242" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H242" t="s">
+        <v>17</v>
+      </c>
+      <c r="I242">
+        <v>42</v>
+      </c>
+      <c r="J242">
+        <v>8001</v>
+      </c>
+      <c r="K242" t="s">
+        <v>17</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>0</v>
+      </c>
+      <c r="P242">
+        <v>0</v>
+      </c>
+      <c r="Q242">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>130740205</v>
+      </c>
+      <c r="B243" t="s">
+        <v>17</v>
+      </c>
+      <c r="C243" t="s">
+        <v>17</v>
+      </c>
+      <c r="D243" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243">
+        <v>1211</v>
+      </c>
+      <c r="F243" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G243" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H243" t="s">
+        <v>17</v>
+      </c>
+      <c r="I243">
+        <v>42</v>
+      </c>
+      <c r="J243">
+        <v>8001</v>
+      </c>
+      <c r="K243" t="s">
+        <v>17</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>0</v>
+      </c>
+      <c r="O243">
+        <v>0</v>
+      </c>
+      <c r="P243">
+        <v>0</v>
+      </c>
+      <c r="Q243">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>130740209</v>
+      </c>
+      <c r="B244" t="s">
+        <v>17</v>
+      </c>
+      <c r="C244" t="s">
+        <v>17</v>
+      </c>
+      <c r="D244" t="s">
+        <v>17</v>
+      </c>
+      <c r="E244">
+        <v>1211</v>
+      </c>
+      <c r="F244" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G244" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H244" t="s">
+        <v>17</v>
+      </c>
+      <c r="I244">
+        <v>42</v>
+      </c>
+      <c r="J244">
+        <v>8001</v>
+      </c>
+      <c r="K244" t="s">
+        <v>17</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>0</v>
+      </c>
+      <c r="O244">
+        <v>0</v>
+      </c>
+      <c r="P244">
+        <v>0</v>
+      </c>
+      <c r="Q244">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>130740211</v>
+      </c>
+      <c r="B245" t="s">
+        <v>17</v>
+      </c>
+      <c r="C245" t="s">
+        <v>17</v>
+      </c>
+      <c r="D245" t="s">
+        <v>17</v>
+      </c>
+      <c r="E245">
+        <v>1211</v>
+      </c>
+      <c r="F245" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G245" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H245" t="s">
+        <v>17</v>
+      </c>
+      <c r="I245">
+        <v>42</v>
+      </c>
+      <c r="J245">
+        <v>8001</v>
+      </c>
+      <c r="K245" t="s">
+        <v>17</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245">
+        <v>0</v>
+      </c>
+      <c r="P245">
+        <v>0</v>
+      </c>
+      <c r="Q245">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>130740226</v>
+      </c>
+      <c r="B246" t="s">
+        <v>17</v>
+      </c>
+      <c r="C246" t="s">
+        <v>17</v>
+      </c>
+      <c r="D246" t="s">
+        <v>17</v>
+      </c>
+      <c r="E246">
+        <v>1211</v>
+      </c>
+      <c r="F246" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G246" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H246" t="s">
+        <v>17</v>
+      </c>
+      <c r="I246">
+        <v>42</v>
+      </c>
+      <c r="J246">
+        <v>8001</v>
+      </c>
+      <c r="K246" t="s">
+        <v>17</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246">
+        <v>0</v>
+      </c>
+      <c r="P246">
+        <v>0</v>
+      </c>
+      <c r="Q246">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>130740227</v>
+      </c>
+      <c r="B247" t="s">
+        <v>17</v>
+      </c>
+      <c r="C247" t="s">
+        <v>17</v>
+      </c>
+      <c r="D247" t="s">
+        <v>17</v>
+      </c>
+      <c r="E247">
+        <v>1211</v>
+      </c>
+      <c r="F247" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G247" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H247" t="s">
+        <v>17</v>
+      </c>
+      <c r="I247">
+        <v>42</v>
+      </c>
+      <c r="J247">
+        <v>8001</v>
+      </c>
+      <c r="K247" t="s">
+        <v>17</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>0</v>
+      </c>
+      <c r="O247">
+        <v>0</v>
+      </c>
+      <c r="P247">
+        <v>0</v>
+      </c>
+      <c r="Q247">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>130740247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>17</v>
+      </c>
+      <c r="C248" t="s">
+        <v>17</v>
+      </c>
+      <c r="D248" t="s">
+        <v>17</v>
+      </c>
+      <c r="E248">
+        <v>1211</v>
+      </c>
+      <c r="F248" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G248" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H248" t="s">
+        <v>17</v>
+      </c>
+      <c r="I248">
+        <v>42</v>
+      </c>
+      <c r="J248">
+        <v>8001</v>
+      </c>
+      <c r="K248" t="s">
+        <v>17</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>0</v>
+      </c>
+      <c r="O248">
+        <v>0</v>
+      </c>
+      <c r="P248">
+        <v>0</v>
+      </c>
+      <c r="Q248">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>130740263</v>
+      </c>
+      <c r="B249" t="s">
+        <v>17</v>
+      </c>
+      <c r="C249" t="s">
+        <v>17</v>
+      </c>
+      <c r="D249" t="s">
+        <v>17</v>
+      </c>
+      <c r="E249">
+        <v>1211</v>
+      </c>
+      <c r="F249" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G249" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H249" t="s">
+        <v>17</v>
+      </c>
+      <c r="I249">
+        <v>42</v>
+      </c>
+      <c r="J249">
+        <v>8001</v>
+      </c>
+      <c r="K249" t="s">
+        <v>17</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>0</v>
+      </c>
+      <c r="O249">
+        <v>0</v>
+      </c>
+      <c r="P249">
+        <v>0</v>
+      </c>
+      <c r="Q249">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>130740266</v>
+      </c>
+      <c r="B250" t="s">
+        <v>17</v>
+      </c>
+      <c r="C250" t="s">
+        <v>17</v>
+      </c>
+      <c r="D250" t="s">
+        <v>17</v>
+      </c>
+      <c r="E250">
+        <v>1211</v>
+      </c>
+      <c r="F250" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G250" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H250" t="s">
+        <v>17</v>
+      </c>
+      <c r="I250">
+        <v>42</v>
+      </c>
+      <c r="J250">
+        <v>8001</v>
+      </c>
+      <c r="K250" t="s">
+        <v>17</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250">
+        <v>0</v>
+      </c>
+      <c r="P250">
+        <v>0</v>
+      </c>
+      <c r="Q250">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>130740271</v>
+      </c>
+      <c r="B251" t="s">
+        <v>17</v>
+      </c>
+      <c r="C251" t="s">
+        <v>17</v>
+      </c>
+      <c r="D251" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251">
+        <v>1212</v>
+      </c>
+      <c r="F251" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G251" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H251" t="s">
+        <v>17</v>
+      </c>
+      <c r="I251">
+        <v>42</v>
+      </c>
+      <c r="J251">
+        <v>8001</v>
+      </c>
+      <c r="K251" t="s">
+        <v>17</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0</v>
+      </c>
+      <c r="O251">
+        <v>0</v>
+      </c>
+      <c r="P251">
+        <v>0</v>
+      </c>
+      <c r="Q251">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>130740318</v>
+      </c>
+      <c r="B252" t="s">
+        <v>17</v>
+      </c>
+      <c r="C252" t="s">
+        <v>17</v>
+      </c>
+      <c r="D252" t="s">
+        <v>17</v>
+      </c>
+      <c r="E252">
+        <v>2013</v>
+      </c>
+      <c r="F252" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G252" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H252" t="s">
+        <v>17</v>
+      </c>
+      <c r="I252">
+        <v>42</v>
+      </c>
+      <c r="J252">
+        <v>8001</v>
+      </c>
+      <c r="K252" t="s">
+        <v>17</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>0</v>
+      </c>
+      <c r="P252">
+        <v>0</v>
+      </c>
+      <c r="Q252">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>130740323</v>
+      </c>
+      <c r="B253" t="s">
+        <v>17</v>
+      </c>
+      <c r="C253" t="s">
+        <v>17</v>
+      </c>
+      <c r="D253" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253">
+        <v>1211</v>
+      </c>
+      <c r="F253" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G253" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H253" t="s">
+        <v>17</v>
+      </c>
+      <c r="I253">
+        <v>42</v>
+      </c>
+      <c r="J253">
+        <v>8001</v>
+      </c>
+      <c r="K253" t="s">
+        <v>17</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>0</v>
+      </c>
+      <c r="P253">
+        <v>0</v>
+      </c>
+      <c r="Q253">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>130740330</v>
+      </c>
+      <c r="B254" t="s">
+        <v>17</v>
+      </c>
+      <c r="C254" t="s">
+        <v>17</v>
+      </c>
+      <c r="D254" t="s">
+        <v>17</v>
+      </c>
+      <c r="E254">
+        <v>1211</v>
+      </c>
+      <c r="F254" s="1">
+        <v>45651</v>
+      </c>
+      <c r="G254" s="1">
+        <v>45651</v>
+      </c>
+      <c r="H254" t="s">
+        <v>17</v>
+      </c>
+      <c r="I254">
+        <v>42</v>
+      </c>
+      <c r="J254">
+        <v>8001</v>
+      </c>
+      <c r="K254" t="s">
+        <v>17</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>0</v>
+      </c>
+      <c r="O254">
+        <v>0</v>
+      </c>
+      <c r="P254">
+        <v>0</v>
+      </c>
+      <c r="Q254">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>129379286</v>
+      </c>
+      <c r="B255" t="s">
+        <v>17</v>
+      </c>
+      <c r="C255" t="s">
+        <v>17</v>
+      </c>
+      <c r="D255" t="s">
+        <v>17</v>
+      </c>
+      <c r="E255">
+        <v>1211</v>
+      </c>
+      <c r="F255" s="1">
+        <v>45553</v>
+      </c>
+      <c r="G255" s="1">
+        <v>45554</v>
+      </c>
+      <c r="H255" t="s">
+        <v>17</v>
+      </c>
+      <c r="I255">
+        <v>42</v>
+      </c>
+      <c r="J255">
+        <v>8021</v>
+      </c>
+      <c r="K255" t="s">
+        <v>17</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>0</v>
+      </c>
+      <c r="O255">
+        <v>0</v>
+      </c>
+      <c r="P255">
+        <v>0</v>
+      </c>
+      <c r="Q255">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>130492413</v>
+      </c>
+      <c r="B256" t="s">
+        <v>17</v>
+      </c>
+      <c r="C256" t="s">
+        <v>17</v>
+      </c>
+      <c r="D256" t="s">
+        <v>17</v>
+      </c>
+      <c r="E256">
+        <v>1211</v>
+      </c>
+      <c r="F256" s="1">
+        <v>45632</v>
+      </c>
+      <c r="G256" s="1">
+        <v>45633</v>
+      </c>
+      <c r="H256" t="s">
+        <v>17</v>
+      </c>
+      <c r="I256">
+        <v>42</v>
+      </c>
+      <c r="J256">
+        <v>8021</v>
+      </c>
+      <c r="K256" t="s">
+        <v>17</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>0</v>
+      </c>
+      <c r="O256">
+        <v>0</v>
+      </c>
+      <c r="P256">
+        <v>0</v>
+      </c>
+      <c r="Q256">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>130492730</v>
+      </c>
+      <c r="B257" t="s">
+        <v>17</v>
+      </c>
+      <c r="C257" t="s">
+        <v>17</v>
+      </c>
+      <c r="D257" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257">
+        <v>1211</v>
+      </c>
+      <c r="F257" s="1">
+        <v>45632</v>
+      </c>
+      <c r="G257" s="1">
+        <v>45633</v>
+      </c>
+      <c r="H257" t="s">
+        <v>17</v>
+      </c>
+      <c r="I257">
+        <v>42</v>
+      </c>
+      <c r="J257">
+        <v>8021</v>
+      </c>
+      <c r="K257" t="s">
+        <v>17</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257">
+        <v>0</v>
+      </c>
+      <c r="P257">
+        <v>0</v>
+      </c>
+      <c r="Q257">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>130521238</v>
+      </c>
+      <c r="B258" t="s">
+        <v>17</v>
+      </c>
+      <c r="C258" t="s">
+        <v>17</v>
+      </c>
+      <c r="D258" t="s">
+        <v>17</v>
+      </c>
+      <c r="E258">
+        <v>1211</v>
+      </c>
+      <c r="F258" s="1">
+        <v>45635</v>
+      </c>
+      <c r="G258" s="1">
+        <v>45636</v>
+      </c>
+      <c r="H258" t="s">
+        <v>17</v>
+      </c>
+      <c r="I258">
+        <v>42</v>
+      </c>
+      <c r="J258">
+        <v>8021</v>
+      </c>
+      <c r="K258" t="s">
+        <v>17</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>0</v>
+      </c>
+      <c r="P258">
+        <v>0</v>
+      </c>
+      <c r="Q258">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>130554065</v>
+      </c>
+      <c r="B259" t="s">
+        <v>17</v>
+      </c>
+      <c r="C259" t="s">
+        <v>17</v>
+      </c>
+      <c r="D259" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259">
+        <v>1211</v>
+      </c>
+      <c r="F259" s="1">
+        <v>45637</v>
+      </c>
+      <c r="G259" s="1">
+        <v>45638</v>
+      </c>
+      <c r="H259" t="s">
+        <v>17</v>
+      </c>
+      <c r="I259">
+        <v>42</v>
+      </c>
+      <c r="J259">
+        <v>8021</v>
+      </c>
+      <c r="K259" t="s">
+        <v>17</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>0</v>
+      </c>
+      <c r="O259">
+        <v>0</v>
+      </c>
+      <c r="P259">
+        <v>0</v>
+      </c>
+      <c r="Q259">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>130665982</v>
+      </c>
+      <c r="B260" t="s">
+        <v>17</v>
+      </c>
+      <c r="C260" t="s">
+        <v>17</v>
+      </c>
+      <c r="D260" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260">
+        <v>2013</v>
+      </c>
+      <c r="F260" s="1">
+        <v>45644</v>
+      </c>
+      <c r="G260" s="1">
+        <v>45645</v>
+      </c>
+      <c r="H260" t="s">
+        <v>17</v>
+      </c>
+      <c r="I260">
+        <v>42</v>
+      </c>
+      <c r="J260">
+        <v>8021</v>
+      </c>
+      <c r="K260" t="s">
+        <v>17</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>0</v>
+      </c>
+      <c r="Q260">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>130708995</v>
+      </c>
+      <c r="B261" t="s">
+        <v>17</v>
+      </c>
+      <c r="C261" t="s">
+        <v>17</v>
+      </c>
+      <c r="D261" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261">
+        <v>2013</v>
+      </c>
+      <c r="F261" s="1">
         <v>45646</v>
       </c>
-      <c r="G238" s="1">
-        <v>45646</v>
-      </c>
-      <c r="H238" t="s">
-        <v>17</v>
-      </c>
-      <c r="I238">
-        <v>42</v>
-      </c>
-      <c r="J238">
+      <c r="G261" s="1">
+        <v>45647</v>
+      </c>
+      <c r="H261" t="s">
+        <v>17</v>
+      </c>
+      <c r="I261">
+        <v>42</v>
+      </c>
+      <c r="J261">
+        <v>8021</v>
+      </c>
+      <c r="K261" t="s">
+        <v>17</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
+      </c>
+      <c r="N261">
+        <v>0</v>
+      </c>
+      <c r="O261">
+        <v>0</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>130717122</v>
+      </c>
+      <c r="B262" t="s">
+        <v>17</v>
+      </c>
+      <c r="C262" t="s">
+        <v>17</v>
+      </c>
+      <c r="D262" t="s">
+        <v>17</v>
+      </c>
+      <c r="E262">
+        <v>2013</v>
+      </c>
+      <c r="F262" s="1">
+        <v>45649</v>
+      </c>
+      <c r="G262" s="1">
+        <v>45650</v>
+      </c>
+      <c r="H262" t="s">
+        <v>17</v>
+      </c>
+      <c r="I262">
+        <v>42</v>
+      </c>
+      <c r="J262">
         <v>718</v>
       </c>
-      <c r="K238" t="s">
-        <v>17</v>
-      </c>
-      <c r="L238">
-        <v>0</v>
-      </c>
-      <c r="M238">
-        <v>0</v>
-      </c>
-      <c r="N238">
-        <v>0</v>
-      </c>
-      <c r="O238">
-        <v>0</v>
-      </c>
-      <c r="P238">
-        <v>0</v>
-      </c>
-      <c r="Q238">
+      <c r="K262" t="s">
+        <v>17</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0</v>
+      </c>
+      <c r="Q262">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>130717206</v>
+      </c>
+      <c r="B263" t="s">
+        <v>17</v>
+      </c>
+      <c r="C263" t="s">
+        <v>17</v>
+      </c>
+      <c r="D263" t="s">
+        <v>17</v>
+      </c>
+      <c r="E263">
+        <v>2013</v>
+      </c>
+      <c r="F263" s="1">
+        <v>45649</v>
+      </c>
+      <c r="G263" s="1">
+        <v>45650</v>
+      </c>
+      <c r="H263" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263">
+        <v>42</v>
+      </c>
+      <c r="J263">
+        <v>718</v>
+      </c>
+      <c r="K263" t="s">
+        <v>17</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>0</v>
+      </c>
+      <c r="O263">
+        <v>0</v>
+      </c>
+      <c r="P263">
+        <v>0</v>
+      </c>
+      <c r="Q263">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>130718585</v>
+      </c>
+      <c r="B264" t="s">
+        <v>17</v>
+      </c>
+      <c r="C264" t="s">
+        <v>17</v>
+      </c>
+      <c r="D264" t="s">
+        <v>17</v>
+      </c>
+      <c r="E264">
+        <v>2013</v>
+      </c>
+      <c r="F264" s="1">
+        <v>45649</v>
+      </c>
+      <c r="G264" s="1">
+        <v>45650</v>
+      </c>
+      <c r="H264" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264">
+        <v>42</v>
+      </c>
+      <c r="J264">
+        <v>718</v>
+      </c>
+      <c r="K264" t="s">
+        <v>17</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264">
+        <v>0</v>
+      </c>
+      <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0</v>
+      </c>
+      <c r="Q264">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>130726126</v>
+      </c>
+      <c r="B265" t="s">
+        <v>17</v>
+      </c>
+      <c r="C265" t="s">
+        <v>17</v>
+      </c>
+      <c r="D265" t="s">
+        <v>17</v>
+      </c>
+      <c r="E265">
+        <v>2013</v>
+      </c>
+      <c r="F265" s="1">
+        <v>45649</v>
+      </c>
+      <c r="G265" s="1">
+        <v>45649</v>
+      </c>
+      <c r="H265" t="s">
+        <v>17</v>
+      </c>
+      <c r="I265">
+        <v>42</v>
+      </c>
+      <c r="J265">
+        <v>718</v>
+      </c>
+      <c r="K265" t="s">
+        <v>17</v>
+      </c>
+      <c r="L265">
+        <v>0</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
+      </c>
+      <c r="N265">
+        <v>0</v>
+      </c>
+      <c r="O265">
+        <v>0</v>
+      </c>
+      <c r="P265">
+        <v>0</v>
+      </c>
+      <c r="Q265">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel (1).XLSX
+++ b/Treinamento/Fiel (1).XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$17</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$107</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131981412</v>
+        <v>131967544</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -562,10 +562,10 @@
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45748</v>
+        <v>45751</v>
       </c>
       <c r="G2" s="1">
-        <v>45748</v>
+        <v>45751</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -574,7 +574,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131981283</v>
+        <v>131992592</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -618,10 +618,10 @@
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="G3" s="1">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131981731</v>
+        <v>132012706</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,10 +674,10 @@
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="G4" s="1">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -686,7 +686,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131983346</v>
+        <v>132012709</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -730,10 +730,10 @@
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="G5" s="1">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -742,7 +742,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131957773</v>
+        <v>132012716</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -783,13 +783,13 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="G6" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -798,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8013</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131963979</v>
+        <v>132012729</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -839,13 +839,13 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="G7" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -854,7 +854,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>1735</v>
+        <v>8013</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131965386</v>
+        <v>132023308</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -895,13 +895,13 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="G8" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -910,7 +910,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131965973</v>
+        <v>132043180</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -951,13 +951,13 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45747</v>
+        <v>45751</v>
       </c>
       <c r="G9" s="1">
-        <v>45747</v>
+        <v>45751</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131968389</v>
+        <v>132000449</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1007,13 +1007,13 @@
         <v>24</v>
       </c>
       <c r="E10">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F10" s="1">
-        <v>45747</v>
+        <v>45749</v>
       </c>
       <c r="G10" s="1">
-        <v>45747</v>
+        <v>45749</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1022,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131970952</v>
+        <v>132008878</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1063,13 +1063,13 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F11" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="G11" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
@@ -1078,7 +1078,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>123058958</v>
+        <v>132010412</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1119,13 +1119,13 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F12" s="1">
-        <v>44993</v>
+        <v>45750</v>
       </c>
       <c r="G12" s="1">
-        <v>44995</v>
+        <v>45750</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -1134,7 +1134,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131823527</v>
+        <v>132014212</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1175,13 +1175,13 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F13" s="1">
-        <v>45736</v>
+        <v>45750</v>
       </c>
       <c r="G13" s="1">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
@@ -1190,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131974847</v>
+        <v>131994713</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1231,13 +1231,13 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="G14" s="1">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
@@ -1246,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>132008720</v>
+        <v>131995876</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1287,13 +1287,13 @@
         <v>24</v>
       </c>
       <c r="E15">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45750</v>
+        <v>45749</v>
       </c>
       <c r="G15" s="1">
-        <v>45750</v>
+        <v>45749</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1302,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -1325,16 +1325,13 @@
       <c r="Q15">
         <v>61</v>
       </c>
-      <c r="R15">
-        <v>3</v>
-      </c>
       <c r="S15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>132008846</v>
+        <v>131996094</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1346,13 +1343,13 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45750</v>
+        <v>45749</v>
       </c>
       <c r="G16" s="1">
-        <v>45750</v>
+        <v>45749</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1361,7 +1358,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K16" t="s">
         <v>24</v>
@@ -1384,16 +1381,13 @@
       <c r="Q16">
         <v>61</v>
       </c>
-      <c r="R16">
-        <v>3</v>
-      </c>
       <c r="S16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>132016348</v>
+        <v>131999719</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -1405,48 +1399,5115 @@
         <v>24</v>
       </c>
       <c r="E17">
+        <v>601</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>42</v>
+      </c>
+      <c r="J17">
+        <v>8004</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>61</v>
+      </c>
+      <c r="S17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>132003787</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>601</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>8004</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>61</v>
+      </c>
+      <c r="S18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>132004698</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>601</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>42</v>
+      </c>
+      <c r="J19">
+        <v>8004</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>61</v>
+      </c>
+      <c r="S19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>132008632</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>601</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>42</v>
+      </c>
+      <c r="J20">
+        <v>8004</v>
+      </c>
+      <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>61</v>
+      </c>
+      <c r="S20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>132010031</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21">
+        <v>601</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>42</v>
+      </c>
+      <c r="J21">
+        <v>8004</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>61</v>
+      </c>
+      <c r="S21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>132014059</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>601</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>42</v>
+      </c>
+      <c r="J22">
+        <v>8004</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>61</v>
+      </c>
+      <c r="S22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>132015917</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>601</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>8004</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>61</v>
+      </c>
+      <c r="S23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>132031875</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>601</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24">
+        <v>42</v>
+      </c>
+      <c r="J24">
+        <v>8004</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>61</v>
+      </c>
+      <c r="S24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>131975566</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>1211</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45748</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45748</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25">
+        <v>42</v>
+      </c>
+      <c r="J25">
+        <v>1735</v>
+      </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>61</v>
+      </c>
+      <c r="S25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>131986398</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>1211</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45748</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45748</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>1735</v>
+      </c>
+      <c r="K26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>61</v>
+      </c>
+      <c r="S26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>131986972</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27">
+        <v>1211</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45748</v>
+      </c>
+      <c r="G27" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27">
+        <v>42</v>
+      </c>
+      <c r="J27">
+        <v>1735</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>61</v>
+      </c>
+      <c r="S27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>131990244</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28">
+        <v>1211</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45748</v>
+      </c>
+      <c r="G28" s="1">
+        <v>45748</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28">
+        <v>42</v>
+      </c>
+      <c r="J28">
+        <v>1735</v>
+      </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+      <c r="S28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>131991190</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29">
+        <v>42</v>
+      </c>
+      <c r="J29">
+        <v>1735</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>61</v>
+      </c>
+      <c r="S29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>131992126</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>1212</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>1735</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>61</v>
+      </c>
+      <c r="S30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>131997736</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31">
+        <v>1212</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G31" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>1735</v>
+      </c>
+      <c r="K31" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>61</v>
+      </c>
+      <c r="S31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>131998802</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G32" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>1735</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+      <c r="S32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>132000857</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G33" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>1735</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+      <c r="S33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>132001082</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45749</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>1735</v>
+      </c>
+      <c r="K34" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+      <c r="S34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>132009776</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>1735</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+      <c r="S35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>132019690</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G36" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>1735</v>
+      </c>
+      <c r="K36" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+      <c r="S36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>132022619</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G37" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>1735</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+      <c r="S37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>132024544</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38">
+        <v>1212</v>
+      </c>
+      <c r="F38" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G38" s="1">
+        <v>45750</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>1735</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+      <c r="S38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>123058958</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44993</v>
+      </c>
+      <c r="G39" s="1">
+        <v>44995</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8001</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+      <c r="S39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>131823527</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G40" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8021</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+      <c r="S40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>127761099</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G41" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8001</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+      <c r="S41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>127992029</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G42" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8001</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+      <c r="S42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>128195310</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G43" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8001</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+      <c r="S43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>128247488</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G44" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8001</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+      <c r="S44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>128279978</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G45" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8001</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+      <c r="S45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>128281702</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G46" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8001</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+      <c r="S46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>128374783</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G47" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8001</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+      <c r="S47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>128420620</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G48" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>8001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+      <c r="S48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>128500823</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G49" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8001</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+      <c r="S49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>128584280</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+      <c r="S50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>128666306</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G51" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+      <c r="S51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>128782194</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G52" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+      <c r="S52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>128910122</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G53" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+      <c r="S53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>129149129</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G54" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H54" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8001</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+      <c r="S54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>129228558</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G55" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+      <c r="S55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>129338375</v>
+      </c>
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G56" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8001</v>
+      </c>
+      <c r="K56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+      <c r="S56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>129450712</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G57" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8001</v>
+      </c>
+      <c r="K57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+      <c r="S57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>129474153</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G58" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+      <c r="S58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>129966707</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H59" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8001</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+      <c r="S59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>130030310</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G60" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+      <c r="S60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>130211186</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G61" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+      <c r="S61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>130254415</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G62" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+      <c r="S62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>130270837</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45750</v>
+      </c>
+      <c r="G63" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+      <c r="S63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>130388405</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G64" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+      <c r="S64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>130416067</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G65" s="1">
+        <v>45752</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+      <c r="S65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>130586538</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G66" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+      <c r="S66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>130643707</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+      <c r="S67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>130763998</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68">
+        <v>1211</v>
+      </c>
+      <c r="F68" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G68" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8001</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+      <c r="S68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>130764662</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+      <c r="S69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>130829640</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G70" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8001</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+      <c r="S70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>130834008</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H71" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+      <c r="S71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>130883556</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+      <c r="S72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>131749265</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G73" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+      <c r="S73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>131786889</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H74" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+      <c r="S74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>131812225</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8001</v>
+      </c>
+      <c r="K75" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+      <c r="S75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>131961355</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8001</v>
+      </c>
+      <c r="K76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+      <c r="S76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>132010402</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H77" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8001</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+      <c r="S77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>132019339</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G78" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+      <c r="S78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>132029611</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79">
         <v>2013</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F79" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G79" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8001</v>
+      </c>
+      <c r="K79" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+      <c r="S79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>132042344</v>
+      </c>
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80">
+        <v>2002</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H80" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8001</v>
+      </c>
+      <c r="K80" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+      <c r="S80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>127761099</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81">
+        <v>1211</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G81" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8001</v>
+      </c>
+      <c r="K81" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+      <c r="S81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>127992029</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+      <c r="S82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>128195310</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83">
+        <v>1211</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G83" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8001</v>
+      </c>
+      <c r="K83" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+      <c r="S83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>128666306</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G84" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H84" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8001</v>
+      </c>
+      <c r="K84" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+      <c r="S84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>129228558</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85">
+        <v>1211</v>
+      </c>
+      <c r="F85" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H85" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8001</v>
+      </c>
+      <c r="K85" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+      <c r="S85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>129338375</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G86" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8001</v>
+      </c>
+      <c r="K86" t="s">
+        <v>24</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+      <c r="S86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>129474153</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87">
+        <v>1211</v>
+      </c>
+      <c r="F87" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H87" t="s">
+        <v>24</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8001</v>
+      </c>
+      <c r="K87" t="s">
+        <v>24</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+      <c r="S87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>129966707</v>
+      </c>
+      <c r="B88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H88" t="s">
+        <v>24</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8001</v>
+      </c>
+      <c r="K88" t="s">
+        <v>24</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+      <c r="S88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>130254415</v>
+      </c>
+      <c r="B89" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H89" t="s">
+        <v>24</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8001</v>
+      </c>
+      <c r="K89" t="s">
+        <v>24</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+      <c r="S89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>130270837</v>
+      </c>
+      <c r="B90" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="1">
         <v>45750</v>
       </c>
-      <c r="G17" s="1">
-        <v>45750</v>
-      </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17">
-        <v>42</v>
-      </c>
-      <c r="J17">
+      <c r="G90" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H90" t="s">
+        <v>24</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8001</v>
+      </c>
+      <c r="K90" t="s">
+        <v>24</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+      <c r="S90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>130764662</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G91" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H91" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8001</v>
+      </c>
+      <c r="K91" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+      <c r="S91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>131786889</v>
+      </c>
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G92" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8001</v>
+      </c>
+      <c r="K92" t="s">
+        <v>24</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+      <c r="S92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>131812225</v>
+      </c>
+      <c r="B93" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G93" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H93" t="s">
+        <v>24</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8001</v>
+      </c>
+      <c r="K93" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+      <c r="S93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>132010402</v>
+      </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G94" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H94" t="s">
+        <v>24</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8001</v>
+      </c>
+      <c r="K94" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+      <c r="S94" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>132019339</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G95" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H95" t="s">
+        <v>24</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+      <c r="S95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>132029611</v>
+      </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96">
+        <v>2013</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G96" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H96" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8001</v>
+      </c>
+      <c r="K96" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+      <c r="S96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>132042344</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97">
+        <v>2002</v>
+      </c>
+      <c r="F97" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H97" t="s">
+        <v>24</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8001</v>
+      </c>
+      <c r="K97" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+      <c r="S97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>132030226</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98">
+        <v>2013</v>
+      </c>
+      <c r="F98" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G98" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H98" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
         <v>718</v>
       </c>
-      <c r="K17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>61</v>
-      </c>
-      <c r="R17">
+      <c r="K98" t="s">
+        <v>24</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+      <c r="R98">
         <v>3</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S98" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>132030667</v>
+      </c>
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99">
+        <v>2013</v>
+      </c>
+      <c r="F99" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G99" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H99" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>718</v>
+      </c>
+      <c r="K99" t="s">
+        <v>24</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+      <c r="R99">
+        <v>3</v>
+      </c>
+      <c r="S99" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>132031671</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100">
+        <v>2013</v>
+      </c>
+      <c r="F100" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G100" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H100" t="s">
+        <v>24</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>718</v>
+      </c>
+      <c r="K100" t="s">
+        <v>24</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+      <c r="R100">
+        <v>3</v>
+      </c>
+      <c r="S100" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>132031836</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101">
+        <v>2013</v>
+      </c>
+      <c r="F101" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G101" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H101" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>718</v>
+      </c>
+      <c r="K101" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+      <c r="R101">
+        <v>3</v>
+      </c>
+      <c r="S101" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>132032258</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102">
+        <v>2013</v>
+      </c>
+      <c r="F102" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G102" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H102" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>718</v>
+      </c>
+      <c r="K102" t="s">
+        <v>24</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+      <c r="R102">
+        <v>3</v>
+      </c>
+      <c r="S102" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>132032566</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103">
+        <v>2013</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G103" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H103" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>718</v>
+      </c>
+      <c r="K103" t="s">
+        <v>24</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+      <c r="R103">
+        <v>3</v>
+      </c>
+      <c r="S103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>132032681</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104">
+        <v>2013</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G104" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H104" t="s">
+        <v>24</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>718</v>
+      </c>
+      <c r="K104" t="s">
+        <v>24</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+      <c r="R104">
+        <v>3</v>
+      </c>
+      <c r="S104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>132032745</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105">
+        <v>2013</v>
+      </c>
+      <c r="F105" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G105" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H105" t="s">
+        <v>24</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>718</v>
+      </c>
+      <c r="K105" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+      <c r="R105">
+        <v>3</v>
+      </c>
+      <c r="S105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>132033436</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106">
+        <v>2013</v>
+      </c>
+      <c r="F106" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G106" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H106" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>718</v>
+      </c>
+      <c r="K106" t="s">
+        <v>24</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+      <c r="R106">
+        <v>3</v>
+      </c>
+      <c r="S106" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>132033522</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107">
+        <v>2013</v>
+      </c>
+      <c r="F107" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G107" s="1">
+        <v>45751</v>
+      </c>
+      <c r="H107" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>718</v>
+      </c>
+      <c r="K107" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+      <c r="R107">
+        <v>3</v>
+      </c>
+      <c r="S107" t="s">
         <v>25</v>
       </c>
     </row>
